--- a/data/知识点.xlsx
+++ b/data/知识点.xlsx
@@ -1,21 +1,30 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
-  <bookViews>
-    <workbookView activeTab="0"/>
-  </bookViews>
-  <sheets>
-    <sheet name="知识点" r:id="rId3" sheetId="1"/>
-  </sheets>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <Application>Apache POI</Application>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-09-29T08:30:50Z</dcterms:created>
+  <dc:creator>Apache POI</dc:creator>
+</cp:coreProperties>
+</file>
+
+<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <property fmtid="{5B77E7CE-EC58-BC6A-FAE8-886BEB80DBEB}" pid="2" name="5B77E7CEEC58BC6AFAE8886BEB80DBEB">
+    <vt:lpwstr>otCYQxs9Dbw2bUEn/Soxv9pYAoWsCRIsU8+gIbxzzmNcJN13+qHIPyWmbF9hFzPHyi2m8DLwi54E5OVVM5pJ0yGmgAiYTaR6oYUdYZxdjep6I9xviFUFZ9aTScfBW9OGC8s5YNc8WPvYAuEfuFLwcx3Q9uPdW7adR7EcE3Q1pVdCfFGXtaJ5tMAfZanvCk5fZA9hTalpi02oKzKvinWAk3eVSBZsCxReqTaYrFcb0zqHMyYgzJQtGHd8e8AyZh0kz7H83b2m32g4awu9MpPgm+G966MkGFVbg3FM31R9Gf52KUzEwnZ8F4XleBObycDPiMewiBl8Hq7+wUN9nvsNYJD7cpgcRhEOFk+YF9KifgeMghOoDgnUf2Qsh8Ted3Buo6z9k8UsVt3l6LLu5zTogdiltZ/9R8cBXSP52TvwlvHxx3AuIpkLDwURfFoFP3Pev/C2IzXSscvYgYkyAuZK2q/eZMBrndwD0+vk9vgt+UKZEMBapPbrMyigvq/W8j3bBvW9/mp8LHuA610UwGLLo2nqxFRgSE/2zHXO6buiWKhZYJEbCVvMeeMWSEHQuvqwZbJwjflyKRf5yeKU2VinSltgHRxjM44c0ksBo1gjtPjwKWfrVcPNZBrHeutE4KXW</vt:lpwstr>
+  </property>
+</Properties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="2">
@@ -88,7 +97,19 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr date1904="false"/>
+  <bookViews>
+    <workbookView activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet name="知识点" r:id="rId3" sheetId="1"/>
+  </sheets>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
